--- a/test_vlm_evalkit_results/levanter_vlm_MME.xlsx
+++ b/test_vlm_evalkit_results/levanter_vlm_MME.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="30">
   <si>
     <t>index</t>
   </si>
@@ -52,6 +52,12 @@
     <t>OCR/0005.jpg</t>
   </si>
   <si>
+    <t>OCR/0006.jpg</t>
+  </si>
+  <si>
+    <t>OCR/0007.jpg</t>
+  </si>
+  <si>
     <t>Is the word in the logo "angie's"? Please answer yes or no.</t>
   </si>
   <si>
@@ -80,6 +86,18 @@
   </si>
   <si>
     <t>Is the word in the logo "dress"? Please answer yes or no.</t>
+  </si>
+  <si>
+    <t>Is the word in the logo "the beatles story liver pool"? Please answer yes or no.</t>
+  </si>
+  <si>
+    <t>Is the word in the logo "the beats story liver pool"? Please answer yes or no.</t>
+  </si>
+  <si>
+    <t>Is the phone number in the picture "0131 555 6363"? Please answer yes or no.</t>
+  </si>
+  <si>
+    <t>Is the phone number in the picture "0137 556 6363"? Please answer yes or no.</t>
   </si>
   <si>
     <t>Yes</t>
@@ -443,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -477,10 +495,10 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -494,10 +512,10 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -511,10 +529,10 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -528,10 +546,10 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -545,10 +563,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -562,10 +580,10 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -579,10 +597,10 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -596,10 +614,10 @@
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -613,10 +631,10 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -630,10 +648,78 @@
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/test_vlm_evalkit_results/levanter_vlm_MME.xlsx
+++ b/test_vlm_evalkit_results/levanter_vlm_MME.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="24">
   <si>
     <t>index</t>
   </si>
@@ -52,12 +52,6 @@
     <t>OCR/0005.jpg</t>
   </si>
   <si>
-    <t>OCR/0006.jpg</t>
-  </si>
-  <si>
-    <t>OCR/0007.jpg</t>
-  </si>
-  <si>
     <t>Is the word in the logo "angie's"? Please answer yes or no.</t>
   </si>
   <si>
@@ -86,18 +80,6 @@
   </si>
   <si>
     <t>Is the word in the logo "dress"? Please answer yes or no.</t>
-  </si>
-  <si>
-    <t>Is the word in the logo "the beatles story liver pool"? Please answer yes or no.</t>
-  </si>
-  <si>
-    <t>Is the word in the logo "the beats story liver pool"? Please answer yes or no.</t>
-  </si>
-  <si>
-    <t>Is the phone number in the picture "0131 555 6363"? Please answer yes or no.</t>
-  </si>
-  <si>
-    <t>Is the phone number in the picture "0137 556 6363"? Please answer yes or no.</t>
   </si>
   <si>
     <t>Yes</t>
@@ -461,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -495,10 +477,13 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -512,10 +497,13 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -529,10 +517,13 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -546,10 +537,13 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -563,10 +557,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -580,10 +577,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -597,10 +597,13 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -614,10 +617,13 @@
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -631,10 +637,13 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -648,78 +657,13 @@
         <v>11</v>
       </c>
       <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
         <v>23</v>
       </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" t="s">
-        <v>29</v>
+      <c r="F11" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
